--- a/output/pdf_financials_xlsx/QCX.xlsx
+++ b/output/pdf_financials_xlsx/QCX.xlsx
@@ -4434,37 +4434,37 @@
         </is>
       </c>
       <c r="B92" s="3" t="n">
-        <v>0</v>
+        <v>1.365768</v>
       </c>
       <c r="C92" s="3" t="n">
-        <v>0</v>
+        <v>1.460021</v>
       </c>
       <c r="D92" s="3" t="n">
-        <v>0</v>
+        <v>1.460021</v>
       </c>
       <c r="E92" s="3" t="n">
-        <v>0</v>
+        <v>1.460021</v>
       </c>
       <c r="F92" s="3" t="n">
-        <v>0</v>
+        <v>1.646627</v>
       </c>
       <c r="G92" s="3" t="n">
-        <v>0</v>
+        <v>1.653827</v>
       </c>
       <c r="H92" s="3" t="n">
-        <v>0</v>
+        <v>2.545095</v>
       </c>
       <c r="I92" s="3" t="n">
-        <v>0</v>
+        <v>2.545095</v>
       </c>
       <c r="J92" s="3" t="n">
-        <v>0</v>
+        <v>2.562067</v>
       </c>
       <c r="K92" s="3" t="n">
-        <v>0</v>
+        <v>2.562067</v>
       </c>
       <c r="L92" s="3" t="n">
-        <v>0</v>
+        <v>2.83182</v>
       </c>
     </row>
     <row r="93">
@@ -5441,10 +5441,10 @@
         </is>
       </c>
       <c r="B118" s="3" t="n">
-        <v>4.974925</v>
+        <v>4.900166</v>
       </c>
       <c r="C118" s="3" t="n">
-        <v>0.045548</v>
+        <v>0.034274</v>
       </c>
       <c r="D118" s="3" t="n">
         <v>-0.013195</v>
@@ -7148,7 +7148,11 @@
           <t>Reserves 8</t>
         </is>
       </c>
-      <c r="D15" t="inlineStr"/>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E15" t="inlineStr">
         <is>
           <t>-</t>
@@ -7628,7 +7632,11 @@
           <t>Reserves 7</t>
         </is>
       </c>
-      <c r="D23" t="inlineStr"/>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E23" t="inlineStr">
         <is>
           <t>-</t>
@@ -8127,7 +8135,11 @@
           <t>Reserves 6</t>
         </is>
       </c>
-      <c r="D30" t="inlineStr"/>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E30" t="inlineStr">
         <is>
           <t>-</t>
@@ -9079,7 +9091,11 @@
           <t>Reserves</t>
         </is>
       </c>
-      <c r="D44" t="inlineStr"/>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E44" s="5" t="n">
         <v>1.365768</v>
       </c>
@@ -13698,7 +13714,11 @@
           <t>Exploration and evaluation asset expenditures</t>
         </is>
       </c>
-      <c r="D111" t="inlineStr"/>
+      <c r="D111" t="inlineStr">
+        <is>
+          <t>NetOtherInvestingChanges</t>
+        </is>
+      </c>
       <c r="E111" t="inlineStr">
         <is>
           <t>-</t>
@@ -14483,7 +14503,11 @@
           <t>Exploration and evaluation asset expenditures</t>
         </is>
       </c>
-      <c r="D122" t="inlineStr"/>
+      <c r="D122" t="inlineStr">
+        <is>
+          <t>NetOtherInvestingChanges</t>
+        </is>
+      </c>
       <c r="E122" s="5" t="n">
         <v>-0.07475900000000001</v>
       </c>

--- a/output/pdf_financials_xlsx/QCX.xlsx
+++ b/output/pdf_financials_xlsx/QCX.xlsx
@@ -2030,16 +2030,16 @@
         </is>
       </c>
       <c r="B34" s="3" t="n">
-        <v>0</v>
+        <v>0.019063</v>
       </c>
       <c r="C34" s="3" t="n">
         <v>0</v>
       </c>
       <c r="D34" s="3" t="n">
-        <v>0</v>
+        <v>0.000186</v>
       </c>
       <c r="E34" s="3" t="n">
-        <v>0</v>
+        <v>7.1e-05</v>
       </c>
       <c r="F34" s="3" t="n">
         <v>0</v>
@@ -2048,19 +2048,19 @@
         <v>0</v>
       </c>
       <c r="H34" s="3" t="n">
-        <v>0</v>
+        <v>0.111036</v>
       </c>
       <c r="I34" s="3" t="n">
-        <v>0</v>
+        <v>0.128203</v>
       </c>
       <c r="J34" s="3" t="n">
-        <v>0</v>
+        <v>0.088813</v>
       </c>
       <c r="K34" s="3" t="n">
-        <v>0</v>
+        <v>0.013002</v>
       </c>
       <c r="L34" s="3" t="n">
-        <v>0</v>
+        <v>0.254333</v>
       </c>
     </row>
     <row r="35">
@@ -2110,16 +2110,16 @@
         </is>
       </c>
       <c r="B36" s="3" t="n">
-        <v>0</v>
+        <v>0.019063</v>
       </c>
       <c r="C36" s="3" t="n">
         <v>0</v>
       </c>
       <c r="D36" s="3" t="n">
-        <v>0</v>
+        <v>0.000186</v>
       </c>
       <c r="E36" s="3" t="n">
-        <v>0</v>
+        <v>7.1e-05</v>
       </c>
       <c r="F36" s="3" t="n">
         <v>0</v>
@@ -2128,19 +2128,19 @@
         <v>0</v>
       </c>
       <c r="H36" s="3" t="n">
-        <v>0</v>
+        <v>0.111036</v>
       </c>
       <c r="I36" s="3" t="n">
-        <v>0</v>
+        <v>0.128203</v>
       </c>
       <c r="J36" s="3" t="n">
-        <v>0</v>
+        <v>0.088813</v>
       </c>
       <c r="K36" s="3" t="n">
-        <v>0</v>
+        <v>0.013002</v>
       </c>
       <c r="L36" s="3" t="n">
-        <v>0</v>
+        <v>0.254333</v>
       </c>
     </row>
     <row r="37">
@@ -2590,16 +2590,16 @@
         </is>
       </c>
       <c r="B48" s="3" t="n">
-        <v>0.02447</v>
+        <v>0.005407</v>
       </c>
       <c r="C48" s="3" t="n">
         <v>0.000736</v>
       </c>
       <c r="D48" s="3" t="n">
-        <v>0.000778</v>
+        <v>0.000592</v>
       </c>
       <c r="E48" s="3" t="n">
-        <v>0.000653</v>
+        <v>0.0005820000000000001</v>
       </c>
       <c r="F48" s="3" t="n">
         <v>0.002745</v>
@@ -2608,19 +2608,19 @@
         <v>0</v>
       </c>
       <c r="H48" s="3" t="n">
-        <v>0.150555</v>
+        <v>0.039519</v>
       </c>
       <c r="I48" s="3" t="n">
-        <v>0.172267</v>
+        <v>0.044064</v>
       </c>
       <c r="J48" s="3" t="n">
-        <v>0.131868</v>
+        <v>0.043055</v>
       </c>
       <c r="K48" s="3" t="n">
-        <v>0.057841</v>
+        <v>0.044839</v>
       </c>
       <c r="L48" s="3" t="n">
-        <v>0.279526</v>
+        <v>0.025193</v>
       </c>
     </row>
     <row r="49">
@@ -6299,7 +6299,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E2" s="5" t="n">

--- a/output/pdf_financials_xlsx/QCX.xlsx
+++ b/output/pdf_financials_xlsx/QCX.xlsx
@@ -3376,37 +3376,37 @@
         </is>
       </c>
       <c r="B67" s="3" t="n">
-        <v>0</v>
+        <v>0.02589</v>
       </c>
       <c r="C67" s="3" t="n">
-        <v>0</v>
+        <v>0.01693</v>
       </c>
       <c r="D67" s="3" t="n">
-        <v>0</v>
+        <v>0.01689</v>
       </c>
       <c r="E67" s="3" t="n">
-        <v>0</v>
+        <v>0.01689</v>
       </c>
       <c r="F67" s="3" t="n">
-        <v>0</v>
+        <v>0.01689</v>
       </c>
       <c r="G67" s="3" t="n">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="H67" s="3" t="n">
-        <v>0</v>
+        <v>0.0725</v>
       </c>
       <c r="I67" s="3" t="n">
-        <v>0</v>
+        <v>0.07528899999999999</v>
       </c>
       <c r="J67" s="3" t="n">
-        <v>0</v>
+        <v>0.07049999999999999</v>
       </c>
       <c r="K67" s="3" t="n">
-        <v>0</v>
+        <v>0.110911</v>
       </c>
       <c r="L67" s="3" t="n">
-        <v>0</v>
+        <v>0.073</v>
       </c>
     </row>
     <row r="68">
@@ -13860,7 +13860,11 @@
           <t>Shares issued for cash</t>
         </is>
       </c>
-      <c r="D113" t="inlineStr"/>
+      <c r="D113" t="inlineStr">
+        <is>
+          <t>CommonStockIssuance</t>
+        </is>
+      </c>
       <c r="E113" t="inlineStr">
         <is>
           <t>-</t>
